--- a/data/agent_outputs.xlsx
+++ b/data/agent_outputs.xlsx
@@ -504,7 +504,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{"tool": "read_calendar", "user_id": "me", "available_slots": ["2025-12-09T09:00:00", "2025-12-10T10:00:00", "2025-12-11T11:00:00", "2025-12-12T12:00:00"], "events": [{"title": "Daily Standup", "time": "2025-12-09T10:00:48.325788"}, {"title": "Project Sync", "time": "2025-12-09T15:00:48.325788"}], "note": "Date hint received: next available"}</t>
+          <t>{"tool": "read_calendar", "user_id": "me", "available_slots": ["2025-12-15T09:00:00", "2025-12-16T10:00:00", "2025-12-17T11:00:00", "2025-12-18T12:00:00"], "events": [{"title": "Daily Standup", "time": "2025-12-15T10:00:10.420130"}, {"title": "Project Sync", "time": "2025-12-15T15:00:10.420130"}], "note": "Date hint received: next available"}</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{"sender": "manager@company.com", "last_observation": {"tool": "read_calendar", "user_id": "me", "available_slots": ["2025-12-09T09:00:00", "2025-12-10T10:00:00", "2025-12-11T11:00:00", "2025-12-12T12:00:00"], "events": [{"title": "Daily Standup", "time": "2025-12-09T10:00:48.325788"}, {"title": "Project Sync", "time": "2025-12-09T15:00:48.325788"}], "note": "Date hint received: next available"}}</t>
+          <t>{"sender": "manager@company.com", "last_observation": {"tool": "read_calendar", "user_id": "me", "available_slots": ["2025-12-15T09:00:00", "2025-12-16T10:00:00", "2025-12-17T11:00:00", "2025-12-18T12:00:00"], "events": [{"title": "Daily Standup", "time": "2025-12-15T10:00:10.420130"}, {"title": "Project Sync", "time": "2025-12-15T15:00:10.420130"}], "note": "Date hint received: next available"}}</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-12-09T19:57:48</t>
+          <t>2025-12-15T17:32:10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>{"tool": "read_calendar", "user_id": "me", "available_slots": ["2025-12-09T09:00:00", "2025-12-10T10:00:00", "2025-12-11T11:00:00", "2025-12-12T12:00:00"], "events": [{"title": "Daily Standup", "time": "2025-12-09T10:00:48.325788"}, {"title": "Project Sync", "time": "2025-12-09T15:00:48.325788"}], "note": "Date hint received: next available"}</t>
+          <t>{"tool": "read_calendar", "user_id": "me", "available_slots": ["2025-12-15T09:00:00", "2025-12-16T10:00:00", "2025-12-17T11:00:00", "2025-12-18T12:00:00"], "events": [{"title": "Daily Standup", "time": "2025-12-15T10:00:10.420130"}, {"title": "Project Sync", "time": "2025-12-15T15:00:10.420130"}], "note": "Date hint received: next available"}</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-12-09T19:57:48</t>
+          <t>2025-12-15T17:32:10</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>{"tool": "read_calendar", "user_id": "me", "available_slots": ["2025-12-09T09:00:00", "2025-12-10T10:00:00", "2025-12-11T11:00:00", "2025-12-12T12:00:00"], "events": [{"title": "Daily Standup", "time": "2025-12-09T10:00:48.325788"}, {"title": "Project Sync", "time": "2025-12-09T15:00:48.325788"}], "note": "Date hint received: next available"}</t>
+          <t>{"tool": "read_calendar", "user_id": "me", "available_slots": ["2025-12-15T09:00:00", "2025-12-16T10:00:00", "2025-12-17T11:00:00", "2025-12-18T12:00:00"], "events": [{"title": "Daily Standup", "time": "2025-12-15T10:00:10.420130"}, {"title": "Project Sync", "time": "2025-12-15T15:00:10.420130"}], "note": "Date hint received: next available"}</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-12-09T19:57:48</t>
+          <t>2025-12-15T17:32:10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>{"tool": "read_calendar", "user_id": "me", "available_slots": ["2025-12-09T09:00:00", "2025-12-10T10:00:00", "2025-12-11T11:00:00", "2025-12-12T12:00:00"], "events": [{"title": "Daily Standup", "time": "2025-12-09T10:00:48.325788"}, {"title": "Project Sync", "time": "2025-12-09T15:00:48.325788"}], "note": "Date hint received: next available"}</t>
+          <t>{"tool": "read_calendar", "user_id": "me", "available_slots": ["2025-12-15T09:00:00", "2025-12-16T10:00:00", "2025-12-17T11:00:00", "2025-12-18T12:00:00"], "events": [{"title": "Daily Standup", "time": "2025-12-15T10:00:10.420130"}, {"title": "Project Sync", "time": "2025-12-15T15:00:10.420130"}], "note": "Date hint received: next available"}</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-12-09T19:57:48</t>
+          <t>2025-12-15T17:32:10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>{"tool": "read_calendar", "user_id": "me", "available_slots": ["2025-12-09T09:00:00", "2025-12-10T10:00:00", "2025-12-11T11:00:00", "2025-12-12T12:00:00"], "events": [{"title": "Daily Standup", "time": "2025-12-09T10:00:48.325788"}, {"title": "Project Sync", "time": "2025-12-09T15:00:48.325788"}], "note": "Date hint received: next available"}</t>
+          <t>{"tool": "read_calendar", "user_id": "me", "available_slots": ["2025-12-15T09:00:00", "2025-12-16T10:00:00", "2025-12-17T11:00:00", "2025-12-18T12:00:00"], "events": [{"title": "Daily Standup", "time": "2025-12-15T10:00:10.420130"}, {"title": "Project Sync", "time": "2025-12-15T15:00:10.420130"}], "note": "Date hint received: next available"}</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-12-09T19:57:48</t>
+          <t>2025-12-15T17:32:10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>{"tool": "read_calendar", "user_id": "me", "available_slots": ["2025-12-09T09:00:00", "2025-12-10T10:00:00", "2025-12-11T11:00:00", "2025-12-12T12:00:00"], "events": [{"title": "Daily Standup", "time": "2025-12-09T10:00:48.325788"}, {"title": "Project Sync", "time": "2025-12-09T15:00:48.325788"}], "note": "Date hint received: next available"}</t>
+          <t>{"tool": "read_calendar", "user_id": "me", "available_slots": ["2025-12-15T09:00:00", "2025-12-16T10:00:00", "2025-12-17T11:00:00", "2025-12-18T12:00:00"], "events": [{"title": "Daily Standup", "time": "2025-12-15T10:00:10.420130"}, {"title": "Project Sync", "time": "2025-12-15T15:00:10.420130"}], "note": "Date hint received: next available"}</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2025-12-09T19:57:48</t>
+          <t>2025-12-15T17:32:10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>{"tool": "read_calendar", "user_id": "me", "available_slots": ["2025-12-09T09:00:00", "2025-12-10T10:00:00", "2025-12-11T11:00:00", "2025-12-12T12:00:00"], "events": [{"title": "Daily Standup", "time": "2025-12-09T10:00:48.325788"}, {"title": "Project Sync", "time": "2025-12-09T15:00:48.325788"}], "note": "Date hint received: next available"}</t>
+          <t>{"tool": "read_calendar", "user_id": "me", "available_slots": ["2025-12-15T09:00:00", "2025-12-16T10:00:00", "2025-12-17T11:00:00", "2025-12-18T12:00:00"], "events": [{"title": "Daily Standup", "time": "2025-12-15T10:00:10.420130"}, {"title": "Project Sync", "time": "2025-12-15T15:00:10.420130"}], "note": "Date hint received: next available"}</t>
         </is>
       </c>
     </row>
@@ -857,28 +857,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-12-09T09:00:00</t>
+          <t>2025-12-15T09:00:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-12-10T10:00:00</t>
+          <t>2025-12-16T10:00:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-12-11T11:00:00</t>
+          <t>2025-12-17T11:00:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-12-12T12:00:00</t>
+          <t>2025-12-18T12:00:00</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-12-09T10:00:53.559315</t>
+          <t>2025-12-15T10:00:28.891321</t>
         </is>
       </c>
     </row>
@@ -914,7 +914,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2025-12-09T15:00:53.559315</t>
+          <t>2025-12-15T15:00:28.891321</t>
         </is>
       </c>
     </row>
